--- a/data/Arisdorf/investment_decision/Arisdorf_MFH_from_2015_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_MFH_from_2015_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,12 +58,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,57 +441,57 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>scen_base_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>scen_base_candidate_unit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -505,33 +506,33 @@
         <v>0.003</v>
       </c>
       <c r="E2" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>21.64663108078002</v>
+        <v>21.15770081980719</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -542,33 +543,33 @@
         <v>0.003</v>
       </c>
       <c r="E3" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="F3" t="n">
-        <v>21.64663108078002</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="G3" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="H3" t="n">
-        <v>22.07427013977262</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="I3" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="J3" t="n">
-        <v>22.0716166119829</v>
+        <v>21.15150672079843</v>
       </c>
       <c r="K3" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>21.64663108078002</v>
+        <v>21.15770081980719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -579,33 +580,33 @@
         <v>0.003</v>
       </c>
       <c r="E4" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="F4" t="n">
-        <v>21.64663108078002</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="G4" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="H4" t="n">
-        <v>22.07427013977262</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="I4" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="J4" t="n">
-        <v>22.0716166119829</v>
+        <v>21.15150672079843</v>
       </c>
       <c r="K4" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>21.64663108078002</v>
+        <v>21.15770081980719</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -616,33 +617,33 @@
         <v>0.003</v>
       </c>
       <c r="E5" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="F5" t="n">
-        <v>21.64663108078002</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="G5" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="H5" t="n">
-        <v>22.07427013977262</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="I5" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="J5" t="n">
-        <v>22.0716166119829</v>
+        <v>21.15150672079843</v>
       </c>
       <c r="K5" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>21.64663108078002</v>
+        <v>21.15770081980719</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -653,29 +654,29 @@
         <v>0.003</v>
       </c>
       <c r="E6" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="F6" t="n">
-        <v>21.64663108078002</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="G6" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="H6" t="n">
-        <v>22.07427013977262</v>
+        <v>19.01813715927825</v>
       </c>
       <c r="I6" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
       <c r="J6" t="n">
-        <v>22.0716166119829</v>
+        <v>21.15150672079843</v>
       </c>
       <c r="K6" t="n">
-        <v>2852.026446984596</v>
+        <v>2850.360061333056</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -690,29 +691,29 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -727,29 +728,29 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -764,29 +765,29 @@
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -801,29 +802,29 @@
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -838,33 +839,33 @@
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.278039670476893</v>
+        <v>4.275540091999584</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.00155312352</v>
+        <v>0.0017256928</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -878,30 +879,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00155312352</v>
+        <v>0.0017256928</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.00155312352</v>
+        <v>0.0017256928</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00155312352</v>
+        <v>0.0017256928</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021968775517317</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -927,18 +928,18 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021422237369486</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021968775517317</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -964,18 +965,18 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021422237369486</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021968775517317</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1001,18 +1002,18 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021422237369486</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021968775517317</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1038,14 +1039,14 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00198454672</v>
+        <v>0.002021422237369486</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
@@ -1082,11 +1083,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.04804681389030226</v>
+        <v>0.08384190526816063</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1100,30 +1101,30 @@
         <v>0.3080361648</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04804681389030226</v>
+        <v>0.08471694189457166</v>
       </c>
       <c r="G18" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04604101598566605</v>
+        <v>0.08471694189457166</v>
       </c>
       <c r="I18" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J18" t="n">
-        <v>0.04612970673061868</v>
+        <v>0.08381263815034425</v>
       </c>
       <c r="K18" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.04804681389030226</v>
+        <v>0.08384190526816063</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1137,30 +1138,30 @@
         <v>0.3080361648</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04804681389030226</v>
+        <v>0.08771613849541011</v>
       </c>
       <c r="G19" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H19" t="n">
-        <v>0.04604101598566605</v>
+        <v>0.08771613849541011</v>
       </c>
       <c r="I19" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04612970673061868</v>
+        <v>0.08381263815034425</v>
       </c>
       <c r="K19" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.128232330321795</v>
+        <v>0.1669471706424935</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1174,30 +1175,30 @@
         <v>0.3080361648</v>
       </c>
       <c r="F20" t="n">
-        <v>0.128232330321795</v>
+        <v>0.1713180117835843</v>
       </c>
       <c r="G20" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H20" t="n">
-        <v>0.128232330321795</v>
+        <v>0.1713180117835843</v>
       </c>
       <c r="I20" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J20" t="n">
-        <v>0.128232330321795</v>
+        <v>0.1669200577055564</v>
       </c>
       <c r="K20" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.08018551643149274</v>
+        <v>0.08310526537433291</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1211,26 +1212,26 @@
         <v>0.3080361648</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08018551643149271</v>
+        <v>0.08660106988901262</v>
       </c>
       <c r="G21" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08219131433612897</v>
+        <v>0.08660106988901262</v>
       </c>
       <c r="I21" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08210262359117633</v>
+        <v>0.08310741955521213</v>
       </c>
       <c r="K21" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1267,7 +1268,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1304,7 +1305,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1341,7 +1342,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1378,7 +1379,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1415,7 +1416,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1452,11 +1453,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.0008750366264110481</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1482,18 +1483,18 @@
         <v>0.3080361648</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.0009043037442274315</v>
       </c>
       <c r="K28" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>0.002144261466413958</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1519,18 +1520,18 @@
         <v>0.3080361648</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>0.002175764081691177</v>
       </c>
       <c r="K29" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.004370841141090771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1556,18 +1557,18 @@
         <v>0.3080361648</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.004397954078027916</v>
       </c>
       <c r="K30" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>0.003495804514679738</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1593,14 +1594,14 @@
         <v>0.3080361648</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.003493650333800474</v>
       </c>
       <c r="K31" t="n">
         <v>0.3080361648</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1637,7 +1638,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1674,7 +1675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1711,7 +1712,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1748,7 +1749,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1785,7 +1786,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1822,7 +1823,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1859,7 +1860,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1896,7 +1897,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1933,7 +1934,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1970,7 +1971,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -2007,7 +2008,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2044,7 +2045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2081,7 +2082,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2118,11 +2119,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>0.8745297313098341</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2155,7 +2156,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2170,33 +2171,33 @@
         <v>0.08</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
-        <v>0.1591127303285617</v>
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2207,33 +2208,33 @@
         <v>0.08</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F48" t="n">
-        <v>0.164862665515798</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H48" t="n">
-        <v>0.1589394274764169</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1650846790734822</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1591127303285617</v>
+        <v>0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2244,33 +2245,33 @@
         <v>0.08</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F49" t="n">
-        <v>0.164862665515798</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1589394274764169</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J49" t="n">
-        <v>0.1650846790734822</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
-        <v>0.1591127303285617</v>
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2281,29 +2282,29 @@
         <v>0.08</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F50" t="n">
-        <v>0.164862665515798</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1589394274764169</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J50" t="n">
-        <v>0.1650846790734822</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2318,29 +2319,29 @@
         <v>0.08</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
@@ -2355,33 +2356,33 @@
         <v>0.08</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.07506702229918218</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2392,33 +2393,33 @@
         <v>0.08</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F53" t="n">
-        <v>0.06931624698460982</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="G53" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H53" t="n">
-        <v>0.07550010701853963</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J53" t="n">
-        <v>0.06935324345832596</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="K53" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.07506702229918218</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2429,33 +2430,33 @@
         <v>0.08</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F54" t="n">
-        <v>0.06931624698460982</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H54" t="n">
-        <v>0.07550010701853961</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J54" t="n">
-        <v>0.06935324345832596</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.07506702229918218</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2466,33 +2467,33 @@
         <v>0.08</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F55" t="n">
-        <v>0.06931624698460982</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H55" t="n">
-        <v>0.07550010701853961</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J55" t="n">
-        <v>0.06935324345832596</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1381785170562705</v>
+        <v>0.1223858553894694</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2503,29 +2504,29 @@
         <v>0.08</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1370466995019729</v>
+        <v>0.125890095210251</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1381785170562705</v>
+        <v>0.1258857035671663</v>
       </c>
       <c r="I56" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1370416198330874</v>
+        <v>0.1252080329480626</v>
       </c>
       <c r="K56" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2540,29 +2541,29 @@
         <v>0.08</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2577,29 +2578,29 @@
         <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2614,29 +2615,29 @@
         <v>0.08</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2651,29 +2652,29 @@
         <v>0.08</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2688,29 +2689,29 @@
         <v>0.08</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2725,33 +2726,33 @@
         <v>0.08</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.00951977126108451</v>
+        <v>0.05018156077713196</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2762,33 +2763,33 @@
         <v>0.08</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F63" t="n">
-        <v>0.009520611388420591</v>
+        <v>0.05034992964863943</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H63" t="n">
-        <v>0.007255431304844075</v>
+        <v>0.05034992964863943</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J63" t="n">
-        <v>0.007269481679506723</v>
+        <v>0.05018401975513074</v>
       </c>
       <c r="K63" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.00951977126108451</v>
+        <v>0.05018156077713196</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2799,33 +2800,33 @@
         <v>0.08</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F64" t="n">
-        <v>0.009520611388420591</v>
+        <v>0.05034992964863943</v>
       </c>
       <c r="G64" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H64" t="n">
-        <v>0.007255431304844075</v>
+        <v>0.05034992964863943</v>
       </c>
       <c r="I64" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J64" t="n">
-        <v>0.007269481679506723</v>
+        <v>0.05018401975513074</v>
       </c>
       <c r="K64" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.00951977126108451</v>
+        <v>0.05018156077713194</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2836,33 +2837,33 @@
         <v>0.08</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F65" t="n">
-        <v>0.009520611388420591</v>
+        <v>0.05034992964863941</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H65" t="n">
-        <v>0.007255431304844075</v>
+        <v>0.05034992964863943</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J65" t="n">
-        <v>0.007269481679506723</v>
+        <v>0.0501840197551307</v>
       </c>
       <c r="K65" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1055210068325579</v>
+        <v>0.06053717347721251</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2873,29 +2874,29 @@
         <v>0.08</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1066528243868554</v>
+        <v>0.05701218047703855</v>
       </c>
       <c r="G66" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H66" t="n">
-        <v>0.1035164487435301</v>
+        <v>0.05701657212012317</v>
       </c>
       <c r="I66" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1046657843782275</v>
+        <v>0.05771708059892965</v>
       </c>
       <c r="K66" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2910,29 +2911,29 @@
         <v>0.08</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2947,29 +2948,29 @@
         <v>0.08</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -2984,29 +2985,29 @@
         <v>0.08</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3021,29 +3022,29 @@
         <v>0.08</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3058,29 +3059,29 @@
         <v>0.08</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3095,29 +3096,29 @@
         <v>0.08</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3132,29 +3133,29 @@
         <v>0.08</v>
       </c>
       <c r="E73" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3169,29 +3170,29 @@
         <v>0.08</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3206,29 +3207,29 @@
         <v>0.08</v>
       </c>
       <c r="E75" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3243,29 +3244,29 @@
         <v>0.08</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="3" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
@@ -3280,29 +3281,29 @@
         <v>0.08</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="3" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
@@ -3317,29 +3318,29 @@
         <v>0.08</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="3" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
@@ -3354,29 +3355,29 @@
         <v>0.08</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="3" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3391,29 +3392,29 @@
         <v>0.08</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="3" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3428,25 +3429,25 @@
         <v>0.08</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.9295135788144713</v>
+        <v>1.245943733304504</v>
       </c>
     </row>
   </sheetData>

--- a/data/Arisdorf/investment_decision/Arisdorf_MFH_from_2015_investment_decision.xlsx
+++ b/data/Arisdorf/investment_decision/Arisdorf_MFH_from_2015_investment_decision.xlsx
@@ -441,52 +441,52 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>scen_base_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>scale_MW</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>scen_base_candidate_unit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_dr_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>scale_MW</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>scen_base_candidate_unit</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_dr_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>21.15770081980719</v>
+        <v>5.826929860997412</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
         <v>2850.360061333056</v>
       </c>
       <c r="F3" t="n">
-        <v>19.01813715927825</v>
+        <v>5.826929860997405</v>
       </c>
       <c r="G3" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="H3" t="n">
-        <v>19.01813715927825</v>
+        <v>5.627312278342568</v>
       </c>
       <c r="I3" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="J3" t="n">
-        <v>21.15150672079843</v>
+        <v>5.826929860997395</v>
       </c>
       <c r="K3" t="n">
         <v>2850.360061333056</v>
@@ -569,7 +569,7 @@
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>21.15770081980719</v>
+        <v>5.826929860997412</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         <v>2850.360061333056</v>
       </c>
       <c r="F4" t="n">
-        <v>19.01813715927825</v>
+        <v>5.826929860997405</v>
       </c>
       <c r="G4" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="H4" t="n">
-        <v>19.01813715927825</v>
+        <v>5.627312278342568</v>
       </c>
       <c r="I4" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="J4" t="n">
-        <v>21.15150672079843</v>
+        <v>5.826929860997395</v>
       </c>
       <c r="K4" t="n">
         <v>2850.360061333056</v>
@@ -606,7 +606,7 @@
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>21.15770081980719</v>
+        <v>5.826929860997412</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,19 +620,19 @@
         <v>2850.360061333056</v>
       </c>
       <c r="F5" t="n">
-        <v>19.01813715927825</v>
+        <v>5.826929860997405</v>
       </c>
       <c r="G5" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="H5" t="n">
-        <v>19.01813715927825</v>
+        <v>5.627312278342568</v>
       </c>
       <c r="I5" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="J5" t="n">
-        <v>21.15150672079843</v>
+        <v>5.826929860997395</v>
       </c>
       <c r="K5" t="n">
         <v>2850.360061333056</v>
@@ -643,7 +643,7 @@
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>21.15770081980719</v>
+        <v>5.826929860997412</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>2850.360061333056</v>
       </c>
       <c r="F6" t="n">
-        <v>19.01813715927825</v>
+        <v>5.826929860997405</v>
       </c>
       <c r="G6" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="H6" t="n">
-        <v>19.01813715927825</v>
+        <v>5.627312278342568</v>
       </c>
       <c r="I6" t="n">
         <v>2850.360061333056</v>
       </c>
       <c r="J6" t="n">
-        <v>21.15150672079843</v>
+        <v>5.826929860997395</v>
       </c>
       <c r="K6" t="n">
         <v>2850.360061333056</v>
@@ -684,32 +684,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
     </row>
     <row r="8">
@@ -721,32 +721,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
     </row>
     <row r="9">
@@ -758,32 +758,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
     </row>
     <row r="10">
@@ -795,32 +795,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
     </row>
     <row r="11">
@@ -832,32 +832,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Arisdorf_b_MFH_from_2015</t>
+          <t>BLVL_Li-ion_s_3 MWh_d_Arisdorf_b_MFH_from_2015</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>4.275540091999584</v>
+        <v>0.03931383707865168</v>
       </c>
     </row>
     <row r="12">
@@ -865,7 +865,7 @@
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0017256928</v>
+        <v>0.001085789745799132</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,19 +879,19 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0017256928</v>
+        <v>0.001085789745799132</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0017256928</v>
+        <v>0.001085789745799132</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0017256928</v>
+        <v>0.001085789745799132</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -902,7 +902,7 @@
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002021968775517317</v>
+        <v>0.00155312352</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.00198454672</v>
+        <v>0.00155312352</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.00198454672</v>
+        <v>0.00155312352</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002021422237369486</v>
+        <v>0.00155312352</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.002021968775517317</v>
+        <v>0.00155312352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,19 +953,19 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.00198454672</v>
+        <v>0.00155312352</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.00198454672</v>
+        <v>0.00155312352</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.002021422237369486</v>
+        <v>0.00155312352</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -976,7 +976,7 @@
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.002021968775517317</v>
+        <v>0.0017256928</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,19 +990,19 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00198454672</v>
+        <v>0.0017256928</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00198454672</v>
+        <v>0.00155312352</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002021422237369486</v>
+        <v>0.00155312352</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002021968775517317</v>
+        <v>0.00189826208</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,19 +1027,19 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00198454672</v>
+        <v>0.00189826208</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.00198454672</v>
+        <v>0.00155312352</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002021422237369486</v>
+        <v>0.00155312352</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
@@ -1087,7 +1087,7 @@
         <v>47849</v>
       </c>
       <c r="B18" t="n">
-        <v>0.08384190526816063</v>
+        <v>0.05777764923483337</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1101,19 +1101,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F18" t="n">
-        <v>0.08471694189457166</v>
+        <v>0.05777764923483342</v>
       </c>
       <c r="G18" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H18" t="n">
-        <v>0.08471694189457166</v>
+        <v>0.05083352750775529</v>
       </c>
       <c r="I18" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J18" t="n">
-        <v>0.08381263815034425</v>
+        <v>0.0491449289861921</v>
       </c>
       <c r="K18" t="n">
         <v>0.3080361648</v>
@@ -1124,7 +1124,7 @@
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0.08384190526816063</v>
+        <v>0.05777764923483337</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,19 +1138,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08771613849541011</v>
+        <v>0.05777764923483342</v>
       </c>
       <c r="G19" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H19" t="n">
-        <v>0.08771613849541011</v>
+        <v>0.05083352750775529</v>
       </c>
       <c r="I19" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08381263815034425</v>
+        <v>0.0491449289861921</v>
       </c>
       <c r="K19" t="n">
         <v>0.3080361648</v>
@@ -1161,7 +1161,7 @@
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1669471706424935</v>
+        <v>0.07401205951040811</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,19 +1175,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1713180117835843</v>
+        <v>0.0758480597204971</v>
       </c>
       <c r="G20" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1713180117835843</v>
+        <v>0.06657414132409063</v>
       </c>
       <c r="I20" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1669200577055564</v>
+        <v>0.06810688259632959</v>
       </c>
       <c r="K20" t="n">
         <v>0.3080361648</v>
@@ -1198,7 +1198,7 @@
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0.08310526537433291</v>
+        <v>0.05777764923483336</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,19 +1212,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08660106988901262</v>
+        <v>0.05814044689818727</v>
       </c>
       <c r="G21" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H21" t="n">
-        <v>0.08660106988901262</v>
+        <v>0.04947481566087448</v>
       </c>
       <c r="I21" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08310741955521213</v>
+        <v>0.04835629759712647</v>
       </c>
       <c r="K21" t="n">
         <v>0.3080361648</v>
@@ -1457,7 +1457,7 @@
         <v>47849</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0008750366264110481</v>
+        <v>0.09167742999999998</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1471,19 +1471,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.09167742999999998</v>
       </c>
       <c r="G28" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.09948646115311917</v>
       </c>
       <c r="I28" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J28" t="n">
-        <v>0.0009043037442274315</v>
+        <v>0.1000565416109343</v>
       </c>
       <c r="K28" t="n">
         <v>0.3080361648</v>
@@ -1494,7 +1494,7 @@
         <v>49675</v>
       </c>
       <c r="B29" t="n">
-        <v>0.002144261466413958</v>
+        <v>0.09307729996936874</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1508,19 +1508,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.0927880347390397</v>
       </c>
       <c r="G29" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.100845173</v>
       </c>
       <c r="I29" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J29" t="n">
-        <v>0.002175764081691177</v>
+        <v>0.1014272694596573</v>
       </c>
       <c r="K29" t="n">
         <v>0.3080361648</v>
@@ -1531,7 +1531,7 @@
         <v>51502</v>
       </c>
       <c r="B30" t="n">
-        <v>0.004370841141090771</v>
+        <v>0.09739830424638621</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1545,19 +1545,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.09556230403629724</v>
       </c>
       <c r="G30" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.1048362224327037</v>
       </c>
       <c r="I30" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J30" t="n">
-        <v>0.004397954078027916</v>
+        <v>0.1033034811604647</v>
       </c>
       <c r="K30" t="n">
         <v>0.3080361648</v>
@@ -1568,7 +1568,7 @@
         <v>53328</v>
       </c>
       <c r="B31" t="n">
-        <v>0.003495804514679738</v>
+        <v>0.09167742999999998</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1582,19 +1582,19 @@
         <v>0.3080361648</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.0916424430076604</v>
       </c>
       <c r="G31" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.100845173</v>
       </c>
       <c r="I31" t="n">
         <v>0.3080361648</v>
       </c>
       <c r="J31" t="n">
-        <v>0.003493650333800474</v>
+        <v>0.100845173</v>
       </c>
       <c r="K31" t="n">
         <v>0.3080361648</v>
@@ -2123,7 +2123,7 @@
         <v>53328</v>
       </c>
       <c r="B46" t="n">
-        <v>0.8745297313098341</v>
+        <v>0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>0.8745297313098341</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>0.8745297313098341</v>
       </c>
       <c r="K46" t="n">
         <v>0.8745297313098341</v>
@@ -2382,7 +2382,7 @@
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1318507334697158</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,19 +2396,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F53" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1310348954053198</v>
       </c>
       <c r="G53" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H53" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1324704542886476</v>
       </c>
       <c r="I53" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J53" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1310348954053199</v>
       </c>
       <c r="K53" t="n">
         <v>1.245943733304504</v>
@@ -2419,7 +2419,7 @@
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1318507334697158</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,19 +2433,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F54" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1310348954053198</v>
       </c>
       <c r="G54" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H54" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1324704542886476</v>
       </c>
       <c r="I54" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J54" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1310348954053199</v>
       </c>
       <c r="K54" t="n">
         <v>1.245943733304504</v>
@@ -2456,7 +2456,7 @@
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1318507334697158</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,19 +2470,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F55" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1310348954053198</v>
       </c>
       <c r="G55" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H55" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1324704542886476</v>
       </c>
       <c r="I55" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J55" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1310348954053199</v>
       </c>
       <c r="K55" t="n">
         <v>1.245943733304504</v>
@@ -2493,7 +2493,7 @@
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1223858553894694</v>
+        <v>0.1277693889250804</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F56" t="n">
-        <v>0.125890095210251</v>
+        <v>0.1249345561491174</v>
       </c>
       <c r="G56" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1258857035671663</v>
+        <v>0.1327745578097047</v>
       </c>
       <c r="I56" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J56" t="n">
-        <v>0.1252080329480626</v>
+        <v>0.1310348954053199</v>
       </c>
       <c r="K56" t="n">
         <v>1.245943733304504</v>
@@ -2752,7 +2752,7 @@
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>0.05018156077713196</v>
+        <v>0.0558389855374021</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,19 +2766,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F63" t="n">
-        <v>0.05034992964863943</v>
+        <v>0.05665482360179815</v>
       </c>
       <c r="G63" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H63" t="n">
-        <v>0.05034992964863943</v>
+        <v>0.05640296278863423</v>
       </c>
       <c r="I63" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J63" t="n">
-        <v>0.05018401975513074</v>
+        <v>0.05665482360179806</v>
       </c>
       <c r="K63" t="n">
         <v>1.245943733304504</v>
@@ -2789,7 +2789,7 @@
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>0.05018156077713196</v>
+        <v>0.0558389855374021</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,19 +2803,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F64" t="n">
-        <v>0.05034992964863943</v>
+        <v>0.05665482360179815</v>
       </c>
       <c r="G64" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H64" t="n">
-        <v>0.05034992964863943</v>
+        <v>0.06430992459970369</v>
       </c>
       <c r="I64" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J64" t="n">
-        <v>0.05018401975513074</v>
+        <v>0.06544048669673203</v>
       </c>
       <c r="K64" t="n">
         <v>1.245943733304504</v>
@@ -2826,7 +2826,7 @@
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>0.05018156077713194</v>
+        <v>0.0558389855374021</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,19 +2840,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F65" t="n">
-        <v>0.05034992964863941</v>
+        <v>0.05665482360179815</v>
       </c>
       <c r="G65" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H65" t="n">
-        <v>0.05034992964863943</v>
+        <v>0.06735936216953971</v>
       </c>
       <c r="I65" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J65" t="n">
-        <v>0.0501840197551307</v>
+        <v>0.06839642333623752</v>
       </c>
       <c r="K65" t="n">
         <v>1.245943733304504</v>
@@ -2863,7 +2863,7 @@
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>0.06053717347721251</v>
+        <v>0.05408008077551825</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,19 +2877,19 @@
         <v>1.245943733304504</v>
       </c>
       <c r="F66" t="n">
-        <v>0.05701218047703855</v>
+        <v>0.0569149135514813</v>
       </c>
       <c r="G66" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="H66" t="n">
-        <v>0.05701657212012317</v>
+        <v>0.06015878473728096</v>
       </c>
       <c r="I66" t="n">
         <v>1.245943733304504</v>
       </c>
       <c r="J66" t="n">
-        <v>0.05771708059892965</v>
+        <v>0.06168222537047156</v>
       </c>
       <c r="K66" t="n">
         <v>1.245943733304504</v>
